--- a/public/template/template_bulk_cheque.xlsx
+++ b/public/template/template_bulk_cheque.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Kerjaan\Bjb\Aplikasi AMT\Back Office\App\Local\bulk_kosongan\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\mtm\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027B3ABF-E1A3-4B14-AFF0-89450BCA8AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F2AC9-806E-4347-A22F-5C72C5771DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,7 +443,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Branch Account" error="Pastikan jumlah karakter tidak lebih dari 4 dan inputan harus berupa angka." promptTitle="Limit Validasi" prompt="Pastikan jumlah karakter tidak lebih dari 4 dan inputan harus berupa angka." sqref="C2:C1048576" xr:uid="{159EB582-111F-43DA-9084-E70C30B0800F}">
       <formula1>4</formula1>
     </dataValidation>
@@ -459,11 +459,14 @@
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Rekening Eksternal" error="Inputan tidak boleh kurang atau lebih dari 13 karakter." promptTitle="Input Validation" prompt="Inputan tidak boleh kurang atau lebih dari 13 karakter." sqref="B2:B1048576" xr:uid="{D63491A6-D9A0-4933-9436-9AC885D3830C}">
       <formula1>13</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." sqref="I2:I1048576" xr:uid="{722273AA-008D-4AFB-9109-1516AC082185}">
-      <formula1>AND(ISERROR(FIND("?",I2)), ISERROR(FIND(":",I2)), ISERROR(FIND("*",I2)))</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 2" error="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." sqref="J2:J1048576" xr:uid="{2602352D-8A01-4165-9A7F-0D398AC81B79}">
-      <formula1>AND(ISERROR(FIND("?",J2)), ISERROR(FIND(":",J2)), ISERROR(FIND("*",J2)))</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." sqref="I3:I1048576" xr:uid="{722273AA-008D-4AFB-9109-1516AC082185}">
+      <formula1>AND(ISERROR(FIND("?",I3)), ISERROR(FIND(":",I3)), ISERROR(FIND("*",I3)))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 2" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="J2:J1048576" xr:uid="{2602352D-8A01-4165-9A7F-0D398AC81B79}">
+      <formula1>AND(ISERROR(FIND("?",J2)), ISERROR(FIND(":",J2)), ISERROR(FIND("*",J2)), LEN(J2)&lt;=35)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="I2" xr:uid="{45999142-0F3B-48B4-B5FD-76E32BE0C9D2}">
+      <formula1>AND(ISERROR(FIND("?",I2)), ISERROR(FIND(":",I2)), ISERROR(FIND("*",I2)), LEN(I2)&lt;=35)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/template/template_bulk_cheque.xlsx
+++ b/public/template/template_bulk_cheque.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\mtm\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\apuppt\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F2AC9-806E-4347-A22F-5C72C5771DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF74C4ED-C326-4F4E-BA40-D974D49632DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,31 +20,25 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Nominal</t>
   </si>
   <si>
-    <t>User Code 1</t>
-  </si>
-  <si>
-    <t>User Code 2</t>
-  </si>
-  <si>
     <t>Keterangan 1</t>
   </si>
   <si>
     <t>Keterangan 2</t>
   </si>
   <si>
-    <t>nomor transaksi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rekening Eksternal </t>
   </si>
   <si>
@@ -55,6 +49,21 @@
   </si>
   <si>
     <t>Suffix Account</t>
+  </si>
+  <si>
+    <t>Refference</t>
+  </si>
+  <si>
+    <t>Cost Center 1</t>
+  </si>
+  <si>
+    <t>Cost Center 2</t>
+  </si>
+  <si>
+    <t>Keterangan 3</t>
+  </si>
+  <si>
+    <t>Keterangan 4</t>
   </si>
 </sst>
 </file>
@@ -397,53 +406,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Branch Account" error="Pastikan jumlah karakter tidak lebih dari 4 dan inputan harus berupa angka." promptTitle="Limit Validasi" prompt="Pastikan jumlah karakter tidak lebih dari 4 dan inputan harus berupa angka." sqref="C2:C1048576" xr:uid="{159EB582-111F-43DA-9084-E70C30B0800F}">
       <formula1>4</formula1>
     </dataValidation>
@@ -459,14 +474,17 @@
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Rekening Eksternal" error="Inputan tidak boleh kurang atau lebih dari 13 karakter." promptTitle="Input Validation" prompt="Inputan tidak boleh kurang atau lebih dari 13 karakter." sqref="B2:B1048576" xr:uid="{D63491A6-D9A0-4933-9436-9AC885D3830C}">
       <formula1>13</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter atau simbol, cukup gunakan teks atau angka." sqref="I3:I1048576" xr:uid="{722273AA-008D-4AFB-9109-1516AC082185}">
-      <formula1>AND(ISERROR(FIND("?",I3)), ISERROR(FIND(":",I3)), ISERROR(FIND("*",I3)))</formula1>
-    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 2" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="J2:J1048576" xr:uid="{2602352D-8A01-4165-9A7F-0D398AC81B79}">
       <formula1>AND(ISERROR(FIND("?",J2)), ISERROR(FIND(":",J2)), ISERROR(FIND("*",J2)), LEN(J2)&lt;=35)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="I2" xr:uid="{45999142-0F3B-48B4-B5FD-76E32BE0C9D2}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="I2:I1048576" xr:uid="{987C1A78-3566-4D23-9C13-B6BE1D088079}">
       <formula1>AND(ISERROR(FIND("?",I2)), ISERROR(FIND(":",I2)), ISERROR(FIND("*",I2)), LEN(I2)&lt;=35)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 3" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="K2:K1048576" xr:uid="{BF88E873-7B31-4A14-B3F0-6FEE63921888}">
+      <formula1>AND(ISERROR(FIND("?",K2)), ISERROR(FIND(":",K2)), ISERROR(FIND("*",K2)), LEN(K2)&lt;=35)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 4" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="L2:L1048576" xr:uid="{A49030DE-28B4-4BD6-B1A4-B7AAA1E0C23A}">
+      <formula1>AND(ISERROR(FIND("?",L2)), ISERROR(FIND(":",L2)), ISERROR(FIND("*",L2)), LEN(L2)&lt;=35)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/template/template_bulk_cheque.xlsx
+++ b/public/template/template_bulk_cheque.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\apuppt\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\cekstatus\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF74C4ED-C326-4F4E-BA40-D974D49632DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E54CB1D-61BC-4E27-BB40-A200CDBA7EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -409,18 +409,18 @@
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -438,10 +438,10 @@
       <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
